--- a/diseases/d178/2026-2029.xlsx
+++ b/diseases/d178/2026-2029.xlsx
@@ -16071,6 +16071,405 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" t="n">
+        <v>1</v>
+      </c>
+      <c r="P82" t="n">
+        <v>1</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>1</v>
+      </c>
+      <c r="O83" t="n">
+        <v>1</v>
+      </c>
+      <c r="P83" t="n">
+        <v>1</v>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN83" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16104,7 +16503,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -16187,7 +16586,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10">
@@ -16197,7 +16596,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11">
@@ -16217,7 +16616,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -16249,7 +16648,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d178/2026-2029.xlsx
+++ b/diseases/d178/2026-2029.xlsx
@@ -16470,6 +16470,405 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP84" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV84" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA84" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC84" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN85" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV85" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA85" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC85" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16503,7 +16902,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -16586,7 +16985,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -16596,7 +16995,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11">
@@ -16616,7 +17015,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d178/2026-2029.xlsx
+++ b/diseases/d178/2026-2029.xlsx
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11416,7 +11416,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12366,13 +12366,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="O62" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="R62" t="n">
-        <v>0.01779337213885181</v>
+        <v>0.02388057839688006</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14100,7 +14100,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14252,13 +14252,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="O72" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="R72" t="n">
-        <v>0.0004682466352329422</v>
+        <v>0.01451564569222121</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15587,7 +15587,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16385,7 +16385,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16498,12 +16498,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -16528,7 +16528,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -16537,98 +16537,81 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>0.003277726446630596</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ84" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -16655,7 +16638,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16707,98 +16690,23 @@
       <c r="P85" t="n">
         <v>0</v>
       </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U85" t="inlineStr">
         <is>
           <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
         </is>
       </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD85" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE85" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF85" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG85" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN85" t="b">
-        <v>1</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -16864,6 +16772,642 @@
         </is>
       </c>
       <c r="BC85" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP86" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV86" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA86" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC86" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV87" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA87" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC87" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN88" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV88" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA88" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB88" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC88" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -16902,7 +17446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -16985,7 +17529,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -16995,7 +17539,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11">
@@ -17015,7 +17559,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
@@ -17047,7 +17591,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d178/2026-2029.xlsx
+++ b/diseases/d178/2026-2029.xlsx
@@ -10586,12 +10586,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -10625,81 +10625,92 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O53" t="n">
-        <v>5</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0.02172846223218448</v>
+        <v>7</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_AFP</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS53" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_AFP</t>
+        </is>
+      </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -10726,17 +10737,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -10761,7 +10772,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -10770,31 +10781,103 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_AFP</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_AFP</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>country:CN-LN:national</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis surveillance syndrome only; not synonymous with poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN54" t="b">
+        <v>1</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -10813,7 +10896,7 @@
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_AFP</t>
         </is>
       </c>
       <c r="AT54" t="n">
@@ -10826,42 +10909,42 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -10888,17 +10971,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -10923,7 +11006,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -10932,173 +11015,81 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD55" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG55" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN55" t="b">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.02172846223218448</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ55" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -11160,7 +11151,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -11169,16 +11160,16 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -11322,7 +11313,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -11331,13 +11322,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -11559,7 +11550,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -11568,16 +11559,16 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -11721,7 +11712,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -11730,13 +11721,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -11958,7 +11949,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -12120,7 +12111,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -12327,12 +12318,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -12357,90 +12348,107 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>51</v>
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>0.02388057839688006</v>
+        <v>0</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS62" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12467,17 +12475,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -12502,90 +12510,182 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>4</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0.01738276978574758</v>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN63" t="b">
+        <v>1</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS63" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12617,12 +12717,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -12647,7 +12747,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -12656,98 +12756,81 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="O64" t="n">
-        <v>1</v>
-      </c>
-      <c r="P64" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="R64" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.02388057839688006</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ64" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS64" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -12774,17 +12857,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -12809,7 +12892,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -12818,106 +12901,25 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O65" t="n">
-        <v>1</v>
-      </c>
-      <c r="P65" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_CN_PROV_REPORT_AFP</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD65" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE65" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF65" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG65" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN65" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -12936,7 +12938,7 @@
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_AFP</t>
         </is>
       </c>
       <c r="AT65" t="n">
@@ -12949,42 +12951,42 @@
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -13011,17 +13013,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -13046,7 +13048,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -13055,31 +13057,103 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_AFP</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_AFP</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>country:CN-LN:national</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis surveillance syndrome only; not synonymous with poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN66" t="b">
+        <v>1</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -13098,7 +13172,7 @@
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_AFP</t>
         </is>
       </c>
       <c r="AT66" t="n">
@@ -13111,42 +13185,42 @@
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -13173,17 +13247,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -13208,7 +13282,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -13217,173 +13291,81 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG67" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN67" t="b">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0.01738276978574758</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ67" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS67" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13445,7 +13427,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -13607,7 +13589,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -13844,7 +13826,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -13853,16 +13835,16 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>0.001633616815131532</v>
+        <v>0</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -14006,7 +13988,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -14015,13 +13997,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -14213,12 +14195,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -14243,90 +14225,107 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="O72" t="n">
-        <v>31</v>
+        <v>1</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>0.01451564569222121</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -14353,17 +14352,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -14388,12 +14387,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -14402,76 +14401,168 @@
       <c r="O73" t="n">
         <v>1</v>
       </c>
-      <c r="R73" t="n">
-        <v>0.004345692446436896</v>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN73" t="b">
+        <v>1</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -14533,25 +14624,25 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R74" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -14695,22 +14786,22 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -14902,12 +14993,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -14932,7 +15023,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -14941,98 +15032,81 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>0.01451564569222121</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ76" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -15059,17 +15133,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -15094,7 +15168,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -15103,173 +15177,81 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD77" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE77" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF77" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG77" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN77" t="b">
         <v>1</v>
       </c>
+      <c r="R77" t="n">
+        <v>0.004345692446436896</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ77" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -15331,7 +15313,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -15493,7 +15475,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -15730,7 +15712,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -15892,7 +15874,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -16129,7 +16111,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -16291,7 +16273,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -16498,12 +16480,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -16528,90 +16510,107 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N84" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>0.003277726446630596</v>
+        <v>0</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16638,7 +16637,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16673,12 +16672,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N85" t="n">
@@ -16690,23 +16689,98 @@
       <c r="P85" t="n">
         <v>0</v>
       </c>
-      <c r="R85" t="n">
-        <v>0</v>
-      </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U85" t="inlineStr">
         <is>
           <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
         </is>
       </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN85" t="b">
+        <v>1</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -16800,7 +16874,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16835,115 +16909,40 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
           <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
         </is>
       </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD86" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE86" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF86" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG86" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN86" t="b">
-        <v>1</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -17037,7 +17036,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -17072,40 +17071,115 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0</v>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
           <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
         </is>
       </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN87" t="b">
+        <v>1</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -17199,215 +17273,921 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>7</v>
+      </c>
+      <c r="O88" t="n">
+        <v>7</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0.003277726446630596</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr"/>
+      <c r="AT88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV88" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA88" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB88" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC88" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP89" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV89" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA89" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC89" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>D178</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>Acute flaccid paralysis</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>急性无力肢体麻痹</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN90" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV90" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA90" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC90" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N88" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="U88" t="inlineStr">
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
         <is>
           <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
         </is>
       </c>
-      <c r="V88" t="inlineStr">
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
         <is>
           <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
         </is>
       </c>
-      <c r="W88" t="inlineStr">
+      <c r="AT91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV91" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC91" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
         <is>
           <t>SRC_JP_NIID</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
+      <c r="Y92" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
+      <c r="Z92" t="inlineStr">
         <is>
           <t>notification</t>
         </is>
       </c>
-      <c r="AA88" t="inlineStr">
+      <c r="AA92" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
+      <c r="AB92" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
+      <c r="AC92" t="inlineStr">
         <is>
           <t>country:JP:national</t>
         </is>
       </c>
-      <c r="AD88" t="inlineStr">
+      <c r="AD92" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE88" t="inlineStr">
+      <c r="AE92" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF88" t="inlineStr">
+      <c r="AF92" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="AG88" t="inlineStr">
+      <c r="AG92" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH88" t="inlineStr">
+      <c r="AH92" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI88" t="inlineStr">
+      <c r="AI92" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ88" t="inlineStr">
+      <c r="AJ92" t="inlineStr">
         <is>
           <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
-      <c r="AK88" t="inlineStr">
+      <c r="AK92" t="inlineStr">
         <is>
           <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
+      <c r="AM92" t="inlineStr">
         <is>
           <t>provisional; raw</t>
         </is>
       </c>
-      <c r="AN88" t="b">
+      <c r="AN92" t="b">
         <v>1</v>
       </c>
-      <c r="AO88" t="inlineStr">
+      <c r="AO92" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP88" t="inlineStr">
+      <c r="AP92" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ88" t="inlineStr">
+      <c r="AQ92" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS88" t="inlineStr">
+      <c r="AS92" t="inlineStr">
         <is>
           <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
         </is>
       </c>
-      <c r="AT88" t="n">
+      <c r="AT92" t="n">
         <v>1</v>
       </c>
-      <c r="AU88" t="inlineStr">
+      <c r="AU92" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV88" t="inlineStr">
+      <c r="AV92" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW88" t="inlineStr">
+      <c r="AW92" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
+      <c r="AX92" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY88" t="inlineStr">
+      <c r="AY92" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
+      <c r="AZ92" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA88" t="inlineStr">
+      <c r="BA92" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB88" t="inlineStr">
+      <c r="BB92" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC88" t="inlineStr">
+      <c r="BC92" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -17529,7 +18309,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
@@ -17539,7 +18319,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11">
@@ -17559,7 +18339,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -17569,7 +18349,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -17591,7 +18371,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>170</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d178/2026-2029.xlsx
+++ b/diseases/d178/2026-2029.xlsx
@@ -18193,6 +18193,405 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC93" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN94" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV94" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18226,7 +18625,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -18309,7 +18708,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -18319,7 +18718,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -18339,7 +18738,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d178/2026-2029.xlsx
+++ b/diseases/d178/2026-2029.xlsx
@@ -773,6 +773,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -909,6 +914,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1045,6 +1055,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1181,6 +1196,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1317,6 +1337,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1453,6 +1478,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1589,6 +1619,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1725,6 +1760,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1861,6 +1901,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1997,6 +2042,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2133,6 +2183,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2269,6 +2324,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2405,6 +2465,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2541,6 +2606,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2677,6 +2747,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2813,6 +2888,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2949,6 +3029,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3085,6 +3170,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3221,6 +3311,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3357,6 +3452,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3493,6 +3593,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3629,6 +3734,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3765,6 +3875,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3901,6 +4016,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4037,6 +4157,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4173,6 +4298,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4309,6 +4439,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4448,6 +4583,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6198,6 +6338,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6334,6 +6479,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6470,6 +6620,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6606,6 +6761,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6742,6 +6902,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6878,6 +7043,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7014,6 +7184,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7150,6 +7325,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7286,6 +7466,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7422,6 +7607,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7558,6 +7748,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7694,6 +7889,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7830,6 +8030,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7966,6 +8171,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8102,6 +8312,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8238,6 +8453,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8374,6 +8594,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8510,6 +8735,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8646,6 +8876,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8782,6 +9017,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8918,6 +9158,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9054,6 +9299,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9190,6 +9440,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9326,6 +9581,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9462,6 +9722,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9598,6 +9863,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9734,6 +10004,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10275,6 +10550,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11626,6 +11906,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11762,6 +12047,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11898,6 +12188,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12034,6 +12329,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12170,6 +12470,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12306,6 +12611,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12442,6 +12752,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12578,6 +12893,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12714,6 +13034,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12850,6 +13175,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12986,6 +13316,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13122,6 +13457,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13258,6 +13598,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13394,6 +13739,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13530,6 +13880,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13666,6 +14021,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13802,6 +14162,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13938,6 +14303,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14074,6 +14444,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14210,6 +14585,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14346,6 +14726,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14482,6 +14867,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14618,6 +15008,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14754,6 +15149,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14890,6 +15290,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15026,6 +15431,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15162,6 +15572,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15703,6 +16118,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17456,6 +17876,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17592,6 +18017,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17728,6 +18158,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17864,6 +18299,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18000,6 +18440,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18136,6 +18581,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18272,6 +18722,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18408,6 +18863,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18544,6 +19004,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18680,6 +19145,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18816,6 +19286,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18952,6 +19427,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19088,6 +19568,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19224,6 +19709,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19360,6 +19850,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19496,6 +19991,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19632,6 +20132,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19768,6 +20273,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19904,6 +20414,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20040,6 +20555,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20176,6 +20696,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20312,6 +20837,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20448,6 +20978,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20584,6 +21119,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20720,6 +21260,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20856,6 +21401,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20992,6 +21542,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21128,6 +21683,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22881,6 +23441,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23026,6 +23591,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23162,6 +23732,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23298,6 +23873,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23434,6 +24014,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23570,6 +24155,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23706,6 +24296,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23842,6 +24437,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23978,6 +24578,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24114,6 +24719,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24250,6 +24860,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24386,6 +25001,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24522,6 +25142,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24658,6 +25283,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24794,6 +25424,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24930,6 +25565,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25066,6 +25706,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25202,6 +25847,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25338,6 +25988,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25474,6 +26129,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25610,6 +26270,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25746,6 +26411,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25882,6 +26552,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26018,6 +26693,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26154,6 +26834,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26290,6 +26975,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26426,6 +27116,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26562,6 +27257,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26698,6 +27398,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28853,6 +29558,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28998,6 +29708,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29134,6 +29849,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29270,6 +29990,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29406,6 +30131,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29542,6 +30272,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29678,6 +30413,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29814,6 +30554,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29950,6 +30695,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30086,6 +30836,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30222,6 +30977,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30358,6 +31118,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30494,6 +31259,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30630,6 +31400,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30766,6 +31541,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30902,6 +31682,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31038,6 +31823,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31174,6 +31964,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31310,6 +32105,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31446,6 +32246,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31582,6 +32387,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31718,6 +32528,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31854,6 +32669,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31990,6 +32810,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32126,6 +32951,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32262,6 +33092,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32398,6 +33233,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32534,6 +33374,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33060,6 +33905,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34801,6 +35651,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34946,6 +35801,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35082,6 +35942,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35218,6 +36083,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35354,6 +36224,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35490,6 +36365,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35626,6 +36506,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35762,6 +36647,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35898,6 +36788,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36034,6 +36929,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36170,6 +37070,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36306,6 +37211,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36442,6 +37352,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36578,6 +37493,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36714,6 +37634,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36850,6 +37775,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36986,6 +37916,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37122,6 +38057,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37258,6 +38198,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37394,6 +38339,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37530,6 +38480,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO246" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37666,6 +38621,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37802,6 +38762,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37938,6 +38903,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38074,6 +39044,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38210,6 +39185,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO251" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38346,6 +39326,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38482,6 +39467,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39008,6 +39998,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40749,6 +41744,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40894,6 +41894,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41030,6 +42035,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41166,6 +42176,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41302,6 +42317,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41438,6 +42458,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41574,6 +42599,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41710,6 +42740,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41846,6 +42881,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41982,6 +43022,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO274" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42118,6 +43163,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42254,6 +43304,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO276" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42390,6 +43445,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO277" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42526,6 +43586,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42662,6 +43727,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO279" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42798,6 +43868,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO280" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42934,6 +44009,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43070,6 +44150,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43206,6 +44291,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO283" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43342,6 +44432,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO284" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43478,6 +44573,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43614,6 +44714,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO286" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43750,6 +44855,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO287" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43886,6 +44996,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO288" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44022,6 +45137,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO289" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44158,6 +45278,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO290" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44294,6 +45419,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO291" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44430,6 +45560,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO292" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44566,6 +45701,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO293" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46706,6 +47846,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO304" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46851,6 +47996,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO305" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46987,6 +48137,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO306" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47123,6 +48278,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO307" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47259,6 +48419,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO308" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47395,6 +48560,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO309" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47531,6 +48701,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO310" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47667,6 +48842,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO311" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47803,6 +48983,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO312" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47939,6 +49124,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO313" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48075,6 +49265,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO314" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48211,6 +49406,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO315" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48347,6 +49547,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO316" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48483,6 +49688,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO317" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48619,6 +49829,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO318" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48755,6 +49970,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO319" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48891,6 +50111,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO320" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49027,6 +50252,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO321" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49163,6 +50393,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO322" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49299,6 +50534,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO323" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49435,6 +50675,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO324" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49571,6 +50816,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO325" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49707,6 +50957,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO326" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49843,6 +51098,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO327" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49979,6 +51239,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO328" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50115,6 +51380,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO329" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50251,6 +51521,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO330" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50385,6 +51660,11 @@
       <c r="S331" t="inlineStr">
         <is>
           <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO331" t="inlineStr">

--- a/diseases/d178/2026-2029.xlsx
+++ b/diseases/d178/2026-2029.xlsx
@@ -53319,6 +53319,405 @@
         </is>
       </c>
     </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N340" t="n">
+        <v>1</v>
+      </c>
+      <c r="O340" t="n">
+        <v>1</v>
+      </c>
+      <c r="P340" t="n">
+        <v>1</v>
+      </c>
+      <c r="R340" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO340" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP340" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ340" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS340" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT340" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU340" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV340" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW340" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX340" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY340" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA340" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB340" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC340" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N341" t="n">
+        <v>1</v>
+      </c>
+      <c r="O341" t="n">
+        <v>1</v>
+      </c>
+      <c r="P341" t="n">
+        <v>1</v>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W341" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X341" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis (excluding acute poliomyelitis)</t>
+        </is>
+      </c>
+      <c r="Y341" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z341" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB341" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC341" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD341" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE341" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF341" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG341" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH341" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI341" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ341" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK341" t="inlineStr">
+        <is>
+          <t>Japan NIID acute flaccid paralysis surveillance syndrome explicitly excluding acute poliomyelitis.</t>
+        </is>
+      </c>
+      <c r="AM341" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN341" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO341" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP341" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ341" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS341" t="inlineStr">
+        <is>
+          <t>SER_JP_AFP_EXCLUDING_POLIO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT341" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU341" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV341" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW341" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX341" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY341" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA341" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB341" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC341" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53352,7 +53751,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -53435,7 +53834,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -53445,7 +53844,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11">
@@ -53465,7 +53864,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -53497,7 +53896,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="16">
